--- a/data/file_generation/input/data_126/工作簿2.xlsx
+++ b/data/file_generation/input/data_126/工作簿2.xlsx
@@ -52853,18 +52853,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{367823F4-C23A-47EE-BD83-35E97072A668}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EAD30EB-2204-4531-A51C-BF3D2DC1EB15}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642C53A2-2D71-4526-9A0C-067063B9356F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF26FD47-3C5F-442C-81AB-900894D42E4F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D8E9FA-3BB4-42BC-AC87-90B12E7EC535}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364CBE84-60B1-4E09-BA3C-2CD4F50027C7}"/>
 </file>